--- a/naver-place-crawler/results_nail/파주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/파주_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오구네일 야당점</t>
+          <t>네일더빛나</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jhl9114@naver.com</t>
+          <t>nail_shine@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1456-0168</t>
+          <t>0507-1328-9181</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 소리천로 25 유은타워7차 A구역 10층 1014호</t>
+          <t>경기도 파주시 한빛로 74 한빛마을5단지 후문상가 110호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Dbtds</t>
+          <t>http://www.instagram.com/nailthebitna</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pznw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>652</v>
+        <v>379</v>
       </c>
       <c r="Q2" t="n">
-        <v>1547</v>
+        <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>2199</v>
+        <v>403</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1449726425</t>
+          <t>1940122686</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449726425</t>
+          <t>https://m.place.naver.com/place/1940122686</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제제뷰티 야당운정점</t>
+          <t>네일빛나다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jejebeauty_@naver.com</t>
+          <t>raronail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1416-0313</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 소리천로 25 유은타워 7차 A동 401호 제제뷰티</t>
+          <t>경기도 파주시 후곡로 21 파워프라자 108호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeje_nail__</t>
+          <t>http://www.instagram.com/nail.bitnada</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,17 +696,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4afk1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>912</v>
+        <v>355</v>
       </c>
       <c r="Q3" t="n">
-        <v>521</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>1433</v>
+        <v>363</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1078123835</t>
+          <t>1477696920</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078123835</t>
+          <t>https://m.place.naver.com/place/1477696920</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일갤러리앤속눈썹 야당점</t>
+          <t>반짝네일스튜디오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>xxooxx0114@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1334-0865</t>
+          <t>0507-1315-2089</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1114 206호 네일갤러리</t>
+          <t>경기도 파주시 가람로116번길 13 6층 602호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgallery_yd</t>
+          <t>https://www.instagram.com/bling_nail.studio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jgbx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1041</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1436</v>
+        <v>67</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1854020265</t>
+          <t>2001534924</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1854020265</t>
+          <t>https://m.place.naver.com/place/2001534924</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>퓨어네일&amp;루나라 슈가링왁싱 파주운정센터</t>
+          <t>모브네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pure_nail_w@naver.com</t>
+          <t>jaera423@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-1536</t>
+          <t>0507-1327-9999</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 30 707호</t>
+          <t>경기도 파주시 해올2길 8 월드타워18차 7층 709호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pure_nail_w</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +874,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vzfi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1118</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1299</v>
+        <v>12</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1552062447</t>
+          <t>2040985876</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552062447</t>
+          <t>https://m.place.naver.com/place/2040985876</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +936,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>운디아네일</t>
+          <t>오구네일 야당점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>undia10@naver.com</t>
+          <t>jhl9114@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-8629</t>
+          <t>0507-1456-0168</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+          <t>경기도 파주시 소리천로 25 유은타워7차 A구역 10층 1014호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/undia_nail</t>
+          <t>http://pf.kakao.com/_Dbtds</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1004,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1823</v>
+        <v>652</v>
       </c>
       <c r="Q6" t="n">
-        <v>166</v>
+        <v>1549</v>
       </c>
       <c r="R6" t="n">
-        <v>1989</v>
+        <v>2201</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1192977296</t>
+          <t>1449726425</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192977296</t>
+          <t>https://m.place.naver.com/place/1449726425</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일로328&amp;슈가링왁싱&amp;눈썹</t>
+          <t>뷰티야</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kingppy@naver.com</t>
+          <t>seoulsba@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1497-0218</t>
+          <t>0507-1349-8459</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 중앙로 328 mh타워 114-A호</t>
+          <t>경기도 파주시 교하로 75 신운정프라차 3차 , 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailro_328</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gxe7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>812</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>829</v>
+        <v>76</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1120611955</t>
+          <t>1080270586</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120611955</t>
+          <t>https://m.place.naver.com/place/1080270586</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>체리누아</t>
+          <t>라봄네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>herseada@naver.com</t>
+          <t>xoxvvvvv@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1327-2939</t>
+          <t>0507-1480-0212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 소리천로 25 214호</t>
+          <t>경기도 파주시 송화로 11 팜스프링 아파트 상가 지하1층 103-2호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherry_noir_nail/</t>
+          <t>http://www.instagram.com/la_bom_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wlcnngb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>382</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2091202986</t>
+          <t>1697955339</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091202986</t>
+          <t>https://m.place.naver.com/place/1697955339</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,34 +1218,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바이유네즈</t>
+          <t>네일파티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>winter-wonderland@naver.com</t>
+          <t>nailpartykorea@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1456-8791</t>
+          <t>0507-1334-4499</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 가람로21번길 62-16 1층102호 바이유네즈 네일스튜디오</t>
+          <t>경기도 파주시 미래로 377</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/byeunej.nail?igsh=MTl2b2lxMmt2bzdheQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://m.blog.naver.com/nailpartykorea</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,19 +1255,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xe0q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>237</v>
+        <v>58</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1252446943</t>
+          <t>1286606170</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252446943</t>
+          <t>https://m.place.naver.com/place/1286606170</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,25 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오모네일</t>
+          <t>네일, 엘렌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wpdbs9015@naver.com</t>
+          <t>tiem6541@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1383-1488</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 번영로 55 새꽃마을 주상가동 205호</t>
+          <t>경기도 파주시 문산읍 방촌로 1744 힐스 1차 후문상가 101호 네일, 엘렌</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/omo__nail/</t>
+          <t>https://www.instagram.com/nail_ellen_?igsh=MWlzY3Nta2VuNHlnaA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1397,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>321</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>347</v>
+        <v>125</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1272846272</t>
+          <t>1062906946</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272846272</t>
+          <t>https://m.place.naver.com/place/1062906946</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1406,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엔유네일</t>
+          <t>네일바이고은</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>xxooxx0114@naver.com</t>
+          <t>yoon_i_blog@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>070-4006-8860</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 파주시 산내로 7 1층</t>
+          <t>경기도 파주시 송화로 11 169동 2층 204호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/by.nu.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1487,34 +1455,4232 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1518532627</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1518532627</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>네일은나</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>banana2z@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1349-9473</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1240번길 30 6층 607호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.eun_na</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="n">
+        <v>147</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1057519985</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057519985</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>무네네일스튜디오 야당점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yojikung@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1303-8757</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1092 유은타워3차 9층 901호.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/munenail_studio</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>643</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>33</v>
+      </c>
+      <c r="R13" t="n">
+        <v>676</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1341223538</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341223538</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>네일블리에</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>s_jhyu_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1381-7231</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1240번길 30 더운정퍼스트 711호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QEnxmG</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>36</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1915725255</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1915725255</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일803</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ball9091@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1438-8030</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올2길 16 107호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/803nail803</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>237</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1079639464</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079639464</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>네일도예쁨</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>hua1349@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1432-9057</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 문산로26번길 13 상가 101동 1-16호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1302886316</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302886316</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네일유 운정야당점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>thgus9800@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1345-2505</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1108 3층 308호 더빛나뷰티 내</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nail._.you</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>144</v>
+      </c>
+      <c r="R17" t="n">
+        <v>238</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1612704270</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1612704270</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>화니네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hblife02@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1422-0319</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 334</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1794741409</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794741409</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>아노 네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>najyun1992@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1363-5474</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 파주시 쇠재2길 32 1F</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>37</v>
+      </c>
+      <c r="R19" t="n">
+        <v>39</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>983355341</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/983355341</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>이안에네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rlathddl8651@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 파주시 법원읍 사임당로 823</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1046351012</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046351012</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>파스텔네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>moon1star6@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>031-945-5554</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 파주시 조리읍 대원로 66 동문상가 1층 119호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1467046877</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1467046877</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>네일아띠</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sisperojinus@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 파주시 초롱꽃로 130 근린생활시설 A동 2층 202호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>14</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2022482530</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2022482530</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>네일공간</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>abzz01@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1333-6892</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 파주시 조리읍 봉천로 38</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/abzz01</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>12</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>815067605</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/815067605</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>써니네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sunnynails_busan@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1349-5524</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 파주시 미래로 562 가람마을9단지남양휴튼상가</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1903298115</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1903298115</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>네일도 빛나게</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>loosetime@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1423-7530</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 파주시 파주읍 우계로 63 . 1층 네일도빛나게</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_shine_chu</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1842693280</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1842693280</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>네일해봄</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>eruriee@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1353-7639</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올2길 16 공감빌딩5층 512호 더시즌태닝샵안</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailhaebom</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>12</v>
+      </c>
+      <c r="R26" t="n">
+        <v>165</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1027271330</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027271330</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>블링블링</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>rhkrdbsk91@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 파주시 시청로 25 광우프라자 2층 203호 블링블링</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/bling_bling6638</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>17</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1343297152</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1343297152</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>네일스튜디오 오홉</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ghh3688@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1345-2966</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 파주시 물향기2로 157 4층 406호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xggDCX</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2006572792</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006572792</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>메이딘네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rubijina@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>031-946-6304</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동패로63번길 36-11</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>24</v>
+      </c>
+      <c r="R29" t="n">
+        <v>44</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>37521041</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37521041</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>네일희</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>arzzang1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1357-4469</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 파주시 초롱꽃로 141 스타타워 B동 307호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__hee?igshid=MzRlODBiNWFlZA==</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>18</v>
+      </c>
+      <c r="R30" t="n">
+        <v>199</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1437954278</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1437954278</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>네일또오세요</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sehe542@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1481-0392</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 파주시 책향기숲길 8 1층 네일 또 오세요</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_comeagain/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>194</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1181698635</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181698635</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>언니쌀롱</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>iheeyoungi@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1465-7833</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 파주시 가재울로 99-16 1층 일부(102)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>http://instagram.com/unni_salon</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>928</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1351</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1277777646</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1277777646</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>라푼젤네일 푸스케어 파주운정점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>fusscare_paju@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1325-1332</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1246 유은타워8차 7층 710호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/fusscare_paju</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>20</v>
+      </c>
+      <c r="R33" t="n">
+        <v>128</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1431106003</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431106003</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>블링네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ks30502000@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1392-8685</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 파주시 번영로 37 유니온프라자 106호 블링네일</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_ExoyUn</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>61</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1230459823</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230459823</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>언니네 네일살롱</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>soyoung7280@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1373-0531</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 사임당로 65-21 정원엘피스타워 101호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://instagram.com/unnine_nailsalon</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>13</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1488218088</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488218088</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>yeju0414@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>031-947-9189</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 파주시 광탄면 큰여울길 24 네일스토리</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>31644250</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31644250</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>그리다네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gridanail2@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1354-7089</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 방촌로 1695-74 남광프라자 302-2호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s6zL66Je</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>15</v>
+      </c>
+      <c r="R37" t="n">
+        <v>144</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1529058149</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1529058149</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>네일은스타</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ejkim0422@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1331-1550</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금바위로 100-1 상가동 1층109호 네일은스타</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>69</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1944569921</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1944569921</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>네일데이</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>honey126@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 사임당로 65-30 1층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QGzlb</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>42</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1961170167</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1961170167</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>원무드네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gogomyyoung@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1369-3781</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로515번길 61 7층 705호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1mood.nail_?igsh=bHc0ZXl3dXF2YmI4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
         <v>19</v>
       </c>
-      <c r="R11" t="n">
-        <v>175</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2059104463</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2059104463</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2069222240</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2069222240</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>코딱지</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dregon010@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>031-941-3771</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 파주시 중앙로 280 장안초원아파트 상가 8호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dregon010</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>33102264</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33102264</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>현네일아트</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lollol5244@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1429-5442</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 파주시 운정로 29 1층 2호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2066585620</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066585620</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>네일포유</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nail_for_u@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 파주시 책향기로 439 상가동 1층 후면 주차장쪽</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail____foryou</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>38</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1083416999</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1083416999</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일바이차차</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>minqlli@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1324-4226</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로 16 상가 113호 네일바이차차</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbycha/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>649</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1460782042</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1460782042</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>haro ,haro</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>fascinoya@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1305-4669</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 파주시 하우고개길 95 1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/haroharo_hi</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>32</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1255712334</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1255712334</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>쏠라네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cherry__pick@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1012 유미어스 오피스텔 상가101호 쏠라네일</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ssolra_nail</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7</v>
+      </c>
+      <c r="R46" t="n">
+        <v>22</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1097774613</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097774613</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>네일위드유</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nail_with_yoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1461-9801</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 파주시 새꽃로 205 2층 네일위드유</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nail._.with_u?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>8</v>
+      </c>
+      <c r="R47" t="n">
+        <v>70</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1359843718</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359843718</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Thenail</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>eksanwl70@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>031-942-7010</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로 80 대보프라자 3층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/eksanwl70</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>35307599</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35307599</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>제이뷰티</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>j_baeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 파주시 심학산로423번길 13-2 102호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/j_baeauty</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>127</v>
+      </c>
+      <c r="R49" t="n">
+        <v>342</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1503778921</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1503778921</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>햅번네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kynkyn37@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>031-946-6322</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1080 명동프라자 1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>18</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>38226612</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38226612</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>오늘보다네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>zpzp9285@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1458-6022</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 파주시 미래로 371 씨티타워 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/oneul.boda.nail</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>74</v>
+      </c>
+      <c r="R51" t="n">
+        <v>293</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>36721481</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36721481</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>케렌시아</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>diadew@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>031-1234-5687</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 파주시 소리천로 25 유은타워 7차 A동 10층 1015호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_querencia</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>9</v>
+      </c>
+      <c r="R52" t="n">
+        <v>12</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1230145456</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230145456</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>네일,다다네</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kssstb539@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1458-4634</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 262 306호 일부</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_dadane/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>21</v>
+      </c>
+      <c r="R53" t="n">
+        <v>115</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1988662305</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1988662305</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>엣지네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>mokpoedgenail@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1341-0303</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금빛로 15 118호(금촌동, 미라클프라자) 엣지네일</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/edge_nail_beauty?igsh=MXFpZTc4OGxocGc0MA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>155</v>
+      </c>
+      <c r="R54" t="n">
+        <v>356</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1621338108</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1621338108</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>네일오브제</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wilklove@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1310-9884</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 파주시 소리천로 25 8층 805호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailobjet_studio?igsh=ZDRpaGV2b3l2dmUy&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>144</v>
+      </c>
+      <c r="R55" t="n">
+        <v>184</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2027658079</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2027658079</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>벨라뷰티</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gmlsend85@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 파주시 광탄면 혜음로 1146-1 1층 벨라뷰티</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sSmnoTQe</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1060147089</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1060147089</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
